--- a/Data/LanternSlot.xlsx
+++ b/Data/LanternSlot.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4B5BD8-B081-4FEE-9AD3-D0EF587EF731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7A9863-B403-4D7A-8E62-BF9C4211150D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5220" yWindow="1455" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lantern" sheetId="1" r:id="rId1"/>
